--- a/table_1_autogenerated.xlsx
+++ b/table_1_autogenerated.xlsx
@@ -653,7 +653,7 @@
     <t xml:space="preserve">InD21</t>
   </si>
   <si>
-    <t xml:space="preserve">89-Type Classification Signature ID</t>
+    <t xml:space="preserve">89/476-Type Classification Signature ID</t>
   </si>
   <si>
     <t xml:space="preserve">Cosine vs Extracted 476-Type Sig Collapsed to 89-Type</t>
